--- a/tests/reports/pytest_report.xlsx
+++ b/tests/reports/pytest_report.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
